--- a/outputs/marine_equipment/Титановые_клапаны.xlsx
+++ b/outputs/marine_equipment/Титановые_клапаны.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Титановая арматура" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Что сделать" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -680,149 +679,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Титан: что нужно выяснить</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Почему</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Сделано</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Проверить наличие</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Позиции числятся по учету от 16.06.2025. До пересчета неизвестно, лежат ли они на складе.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Оценить как изделие</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Титановая судовая арматура дороже бронзовой и стальной того же диаметра. Цену смотрим по чертежам 521-182.110 и 521-182.116 у поставщиков судовой арматуры и на площадках.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Взвесить</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Если изделием не уйдет, титан сдается как цветной лом по весу. Без веса цену лома не посчитать.</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Не отправлять в общий металл</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Титан принимают отдельно и заметно дороже черного лома. В одной куче с чугуном и сталью его оценят по цене черного.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Указывать чертеж в объявлении</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Снабженцы ищут по номеру чертежа, а не по слову «титановый». Чертеж в заголовке объявления работает лучше описания.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Проверить, есть ли еще титан</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>В учете титан указан только в двух строках. При инвентаризации смотреть маркировку: титановая арматура внешне похожа на стальную, но заметно легче.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>